--- a/templates/QUOTATION TEMPLATE.xlsx
+++ b/templates/QUOTATION TEMPLATE.xlsx
@@ -1,24 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Coding\Kintone\Projects\Clavano Excel Export v2.0\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F89A57E8-7832-4869-B686-0E49E5B18C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FB296A-EC77-469D-8909-86E83E695AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{C42AE516-AE06-4823-8788-BA3C80C7942B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C42AE516-AE06-4823-8788-BA3C80C7942B}"/>
   </bookViews>
   <sheets>
-    <sheet name="INPUT DATA" sheetId="1" r:id="rId1"/>
-    <sheet name="QUOTATION TEMPLATE" sheetId="2" r:id="rId2"/>
+    <sheet name="QUOTATION TEMPLATE" sheetId="2" r:id="rId1"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'QUOTATION TEMPLATE'!$A$1:$S$54</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,105 +39,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
   <si>
     <t>DATE</t>
   </si>
   <si>
-    <t>REQUESTED DELIVERY DATE</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>ADDRESS</t>
-  </si>
-  <si>
-    <t>Sales Quotation Number</t>
-  </si>
-  <si>
-    <t>Job Order Number</t>
-  </si>
-  <si>
-    <t>No. Of PAGES:</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>No. of side</t>
-  </si>
-  <si>
-    <t>CONTACT PERSON:</t>
-  </si>
-  <si>
-    <t>CONTACT No.:</t>
-  </si>
-  <si>
-    <t>Email Add:</t>
-  </si>
-  <si>
     <t>Quote No.:</t>
   </si>
   <si>
-    <t>Sales Rep.</t>
-  </si>
-  <si>
-    <t>CECIL ALIGNO</t>
-  </si>
-  <si>
-    <t>ALLOWANCE</t>
-  </si>
-  <si>
-    <t>MARK UP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COVER </t>
-  </si>
-  <si>
-    <t>OFFSET</t>
-  </si>
-  <si>
-    <t>INSIDE PAGES</t>
-  </si>
-  <si>
     <t>DIGITAL</t>
-  </si>
-  <si>
-    <t>COVER-Front</t>
-  </si>
-  <si>
-    <t>COVER-Back (Paper/Color:</t>
-  </si>
-  <si>
-    <t>INSIDE Page (Paper/Color:</t>
-  </si>
-  <si>
-    <t>Finishing</t>
-  </si>
-  <si>
-    <t>ORDER QTY</t>
-  </si>
-  <si>
-    <t>ITEM  DESCRIPTION:</t>
-  </si>
-  <si>
-    <t>SIZE:</t>
-  </si>
-  <si>
-    <t>INPUT SIZE</t>
-  </si>
-  <si>
-    <t>W(INCH)</t>
-  </si>
-  <si>
-    <t>L(INCH)</t>
-  </si>
-  <si>
-    <t>UNIT OF MEASURE:</t>
-  </si>
-  <si>
-    <t>UNIT PRICE:</t>
   </si>
   <si>
     <t>PRICE QUOTATION  / CONTRACT</t>
@@ -273,10 +182,10 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="&quot;₱&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;₱&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="_-[$₱-3409]* #,##0.00_-;\-[$₱-3409]* #,##0.00_-;_-[$₱-3409]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,21 +199,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF1F497D"/>
-      <name val="Century Gothic"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -367,25 +261,41 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDE9D9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCD5B4"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -400,115 +310,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF95B3D7"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF95B3D7"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF95B3D7"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF95B3D7"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF95B3D7"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF95B3D7"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF95B3D7"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF95B3D7"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF95B3D7"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -573,197 +380,133 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="2" borderId="4" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="5" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="10" fillId="0" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="7"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="7"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Heading 4" xfId="3" builtinId="19"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1210,8 +953,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>15949</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>18439</xdr:rowOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>185770</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1301,40 +1044,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="INPUT DATA"/>
-      <sheetName val="QUOTATION OFFSET COST"/>
-      <sheetName val="QUOTATION DIGITAL COST"/>
-      <sheetName val="COSTING  SHEET"/>
-      <sheetName val="POST PRESS"/>
-      <sheetName val="BOM OFFSET"/>
-      <sheetName val="BOM DIGITAL"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="5">
-          <cell r="G5" t="str">
-            <v>CECIL ALIGNO</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1653,739 +1362,418 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D81DEDAE-9C88-49DF-AEAE-88443DF441FA}">
-  <sheetPr>
-    <tabColor theme="5" tint="-0.249977111117893"/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="27.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="7"/>
-    </row>
-    <row r="4" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="7"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="7"/>
-    </row>
-    <row r="7" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-    </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="14"/>
-    </row>
-    <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16"/>
-    </row>
-    <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="18"/>
-    </row>
-    <row r="13" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="18"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="22"/>
-    </row>
-    <row r="15" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="25" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="26"/>
-    </row>
-    <row r="16" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="27" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="30"/>
-    </row>
-    <row r="17" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="30"/>
-    </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-    </row>
-    <row r="19" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="7"/>
-    </row>
-    <row r="20" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="21" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="33"/>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-    </row>
-    <row r="23" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="7"/>
-    </row>
-    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="37" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="35"/>
-      <c r="B25" s="38"/>
-      <c r="C25" s="39"/>
-      <c r="D25" s="40"/>
-    </row>
-    <row r="26" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="7"/>
-    </row>
-  </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B6:D6"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A048E45E-3C9B-4B0E-B986-88BF01AF54D0}">
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="F9:S53"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelCol="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.5546875" style="43" customWidth="1"/>
-    <col min="2" max="3" width="8.88671875" style="43"/>
-    <col min="4" max="4" width="9.6640625" style="43" customWidth="1"/>
-    <col min="5" max="5" width="0.109375" style="43" customWidth="1"/>
-    <col min="6" max="6" width="10.88671875" style="43" customWidth="1"/>
-    <col min="7" max="7" width="2.88671875" style="43" customWidth="1"/>
-    <col min="8" max="8" width="13.6640625" style="43" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="43" customWidth="1"/>
-    <col min="10" max="10" width="40.5546875" style="43" customWidth="1"/>
-    <col min="11" max="11" width="17.109375" style="43" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6640625" style="43" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="13" max="13" width="10.44140625" style="43" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="14" max="14" width="13.109375" style="43" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="15" max="15" width="1.88671875" style="43" customWidth="1" collapsed="1"/>
-    <col min="16" max="16" width="11.109375" style="43" customWidth="1" outlineLevel="1"/>
-    <col min="17" max="17" width="9.5546875" style="43" customWidth="1" outlineLevel="1"/>
-    <col min="18" max="18" width="13.44140625" style="43" customWidth="1" outlineLevel="1"/>
-    <col min="19" max="19" width="2" style="43" customWidth="1"/>
-    <col min="20" max="20" width="9.109375" style="43" customWidth="1"/>
-    <col min="21" max="16384" width="8.88671875" style="43"/>
+    <col min="1" max="1" width="1.5703125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="8.85546875" style="2"/>
+    <col min="4" max="4" width="9.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="0.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="2.85546875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2" customWidth="1"/>
+    <col min="10" max="10" width="40.5703125" style="2" customWidth="1"/>
+    <col min="11" max="11" width="17.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="13" max="13" width="10.42578125" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="14" max="14" width="13.140625" style="2" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="15" max="15" width="1.85546875" style="2" customWidth="1" collapsed="1"/>
+    <col min="16" max="16" width="11.140625" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="17" max="17" width="9.5703125" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="18" max="18" width="13.42578125" style="2" customWidth="1" outlineLevel="1"/>
+    <col min="19" max="19" width="2" style="2" customWidth="1"/>
+    <col min="20" max="20" width="9.140625" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="9" spans="6:19" ht="18" x14ac:dyDescent="0.35">
-      <c r="F9" s="41" t="s">
-        <v>33</v>
-      </c>
-      <c r="G9" s="41"/>
-      <c r="H9" s="41"/>
-      <c r="I9" s="41"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="41"/>
-      <c r="L9" s="41"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="41"/>
-      <c r="O9" s="42"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-    </row>
-    <row r="11" spans="6:19" ht="17.399999999999999" x14ac:dyDescent="0.45">
-      <c r="F11" s="43" t="s">
+    <row r="9" spans="6:19" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F9" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+    </row>
+    <row r="11" spans="6:19" ht="18" x14ac:dyDescent="0.25">
+      <c r="F11" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="G11" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="44">
-        <f>'INPUT DATA'!B1</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="M11" s="46" t="e">
+      <c r="G11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="L11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="M11" s="33" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="N11" s="46"/>
-      <c r="O11" s="47"/>
-      <c r="P11" s="45" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q11" s="46">
-        <f>'INPUT DATA'!B13</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="46"/>
-      <c r="S11" s="47"/>
-    </row>
-    <row r="13" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F13" s="43" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="43">
-        <f>'INPUT DATA'!B10</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="G14" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="48">
-        <f>'INPUT DATA'!B11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="G15" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="49">
-        <f>'INPUT DATA'!B12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F17" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H17" s="43">
-        <f>'INPUT DATA'!B3</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="G18" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H18" s="43">
-        <f>'INPUT DATA'!B4</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="P19" s="50" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-    </row>
-    <row r="20" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F20" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="52"/>
-      <c r="H20" s="53" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" s="53"/>
-      <c r="J20" s="53"/>
-      <c r="K20" s="54"/>
-      <c r="L20" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="M20" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="N20" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="O20" s="55"/>
-      <c r="P20" s="51" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q20" s="51" t="s">
-        <v>40</v>
-      </c>
-      <c r="R20" s="51" t="s">
-        <v>41</v>
-      </c>
-      <c r="S20" s="55"/>
-    </row>
-    <row r="21" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F21" s="56">
+      <c r="N11" s="33"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G21" s="57"/>
-      <c r="H21" s="58">
-        <f>'INPUT DATA'!B23</f>
-        <v>0</v>
-      </c>
-      <c r="I21" s="58"/>
-      <c r="J21" s="59"/>
-      <c r="K21" s="59"/>
-      <c r="L21" s="60" t="e">
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="5"/>
+    </row>
+    <row r="13" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="25"/>
+    </row>
+    <row r="14" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="G14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="26"/>
+    </row>
+    <row r="15" spans="6:19" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="G15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="27"/>
+    </row>
+    <row r="17" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="25"/>
+    </row>
+    <row r="18" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="G18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="25"/>
+    </row>
+    <row r="19" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="P19" s="34" t="s">
+        <v>2</v>
+      </c>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+    </row>
+    <row r="20" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="7"/>
+      <c r="H20" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="N20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="O20" s="8"/>
+      <c r="P20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="R20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="S20" s="8"/>
+    </row>
+    <row r="21" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F21" s="9">
+        <v>1</v>
+      </c>
+      <c r="G21" s="29"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="12" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="M21" s="61" t="e">
+      <c r="M21" s="13" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="N21" s="62" t="e">
+      <c r="N21" s="14" t="e">
         <f>L21*M21</f>
         <v>#REF!</v>
       </c>
-      <c r="O21" s="49"/>
-      <c r="P21" s="60">
-        <f>'INPUT DATA'!B22</f>
-        <v>0</v>
-      </c>
-      <c r="Q21" s="61">
-        <f>'INPUT DATA'!B27</f>
-        <v>0</v>
-      </c>
-      <c r="R21" s="62">
-        <f>P21*Q21</f>
-        <v>0</v>
-      </c>
-      <c r="S21" s="49"/>
-    </row>
-    <row r="22" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="63" t="s">
-        <v>42</v>
-      </c>
-      <c r="I22" s="63"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="59"/>
-      <c r="L22" s="65"/>
-      <c r="M22" s="61"/>
-      <c r="N22" s="62"/>
-      <c r="O22" s="49"/>
-      <c r="P22" s="65"/>
-      <c r="Q22" s="65"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="49"/>
-    </row>
-    <row r="23" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F23" s="56"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="63"/>
-      <c r="J23" s="64">
-        <f>'INPUT DATA'!B25</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="59"/>
-      <c r="L23" s="65"/>
-      <c r="M23" s="61"/>
-      <c r="N23" s="62"/>
-      <c r="O23" s="49"/>
-      <c r="P23" s="65"/>
-      <c r="Q23" s="65"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="49"/>
-    </row>
-    <row r="24" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F24" s="56"/>
-      <c r="G24" s="57"/>
-      <c r="H24" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="63"/>
-      <c r="J24" s="64">
-        <f>'INPUT DATA'!B18</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="59"/>
-      <c r="L24" s="65"/>
-      <c r="M24" s="61"/>
-      <c r="N24" s="62"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="65"/>
-      <c r="Q24" s="65"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="49"/>
-    </row>
-    <row r="25" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="I25" s="63"/>
-      <c r="J25" s="64">
-        <f>'INPUT DATA'!B19</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="59"/>
-      <c r="L25" s="65"/>
-      <c r="M25" s="61"/>
-      <c r="N25" s="62"/>
-      <c r="O25" s="49"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="49"/>
-    </row>
-    <row r="26" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F26" s="56"/>
-      <c r="G26" s="57"/>
-      <c r="H26" s="63" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="63"/>
-      <c r="J26" s="64">
-        <f>'INPUT DATA'!B20</f>
-        <v>0</v>
-      </c>
-      <c r="K26" s="59"/>
-      <c r="L26" s="65"/>
-      <c r="M26" s="61"/>
-      <c r="N26" s="62"/>
-      <c r="O26" s="49"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="66"/>
-      <c r="S26" s="49"/>
-    </row>
-    <row r="27" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F27" s="56"/>
-      <c r="G27" s="57"/>
-      <c r="H27" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="63"/>
-      <c r="J27" s="64">
-        <f>'INPUT DATA'!B7</f>
-        <v>0</v>
-      </c>
-      <c r="K27" s="59"/>
-      <c r="L27" s="65"/>
-      <c r="M27" s="61"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="49"/>
-      <c r="P27" s="65"/>
-      <c r="Q27" s="65"/>
-      <c r="R27" s="66"/>
-      <c r="S27" s="49"/>
-    </row>
-    <row r="28" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F28" s="56"/>
-      <c r="G28" s="57"/>
-      <c r="H28" s="63" t="s">
-        <v>48</v>
-      </c>
-      <c r="I28" s="63"/>
-      <c r="J28" s="64">
-        <f>'INPUT DATA'!B21</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="59"/>
-      <c r="L28" s="65"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="49"/>
-      <c r="P28" s="65"/>
-      <c r="Q28" s="65"/>
-      <c r="R28" s="66"/>
-      <c r="S28" s="49"/>
-    </row>
-    <row r="30" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F30" s="67" t="s">
-        <v>49</v>
-      </c>
-      <c r="G30" s="43" t="s">
+      <c r="O21" s="15"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="38"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="15"/>
+    </row>
+    <row r="22" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F22" s="9"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="I22" s="16"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="17"/>
+      <c r="M22" s="13"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="15"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17"/>
+      <c r="R22" s="18"/>
+      <c r="S22" s="15"/>
+    </row>
+    <row r="23" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F23" s="9"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="I23" s="16"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="17"/>
+      <c r="M23" s="13"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="15"/>
+      <c r="P23" s="17"/>
+      <c r="Q23" s="17"/>
+      <c r="R23" s="18"/>
+      <c r="S23" s="15"/>
+    </row>
+    <row r="24" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F24" s="9"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="I24" s="16"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="17"/>
+      <c r="M24" s="13"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="15"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="17"/>
+      <c r="R24" s="18"/>
+      <c r="S24" s="15"/>
+    </row>
+    <row r="25" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F25" s="9"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I25" s="16"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="13"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="15"/>
+      <c r="P25" s="17"/>
+      <c r="Q25" s="17"/>
+      <c r="R25" s="18"/>
+      <c r="S25" s="15"/>
+    </row>
+    <row r="26" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F26" s="9"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="16"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="17"/>
+      <c r="M26" s="13"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="15"/>
+      <c r="P26" s="17"/>
+      <c r="Q26" s="17"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="15"/>
+    </row>
+    <row r="27" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F27" s="9"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="16"/>
+      <c r="J27" s="28"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="17"/>
+      <c r="M27" s="13"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="17"/>
+      <c r="Q27" s="17"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="15"/>
+    </row>
+    <row r="28" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F28" s="9"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="16"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="11"/>
+      <c r="L28" s="17"/>
+      <c r="M28" s="17"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="15"/>
+      <c r="P28" s="17"/>
+      <c r="Q28" s="17"/>
+      <c r="R28" s="18"/>
+      <c r="S28" s="15"/>
+    </row>
+    <row r="30" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F30" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F31" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="6:19" x14ac:dyDescent="0.25">
+      <c r="F32" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F33" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H33" s="19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F35" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F36" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F37" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F38" s="19" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F40" s="21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="41" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F41" s="22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F43" s="23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="44" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F44" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="48" spans="6:8" x14ac:dyDescent="0.25">
+      <c r="F48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H30" s="67" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F31" s="67" t="s">
-        <v>51</v>
-      </c>
-      <c r="G31" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="67" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="6:19" x14ac:dyDescent="0.3">
-      <c r="F32" s="67" t="s">
-        <v>53</v>
-      </c>
-      <c r="G32" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H32" s="67" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="33" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F33" s="67" t="s">
-        <v>55</v>
-      </c>
-      <c r="G33" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="67" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="35" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F35" s="67" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="36" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F36" s="68" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="37" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F37" s="68" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="38" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F38" s="67" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="40" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F40" s="69" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="41" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F41" s="70" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F43" s="71" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="44" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F44" s="43" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="6:8" x14ac:dyDescent="0.3">
-      <c r="F48" s="43" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="49" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F49" s="67"/>
-    </row>
-    <row r="52" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F52" s="72" t="str">
-        <f>'[1]COSTING  SHEET'!G5</f>
-        <v>CECIL ALIGNO</v>
-      </c>
-    </row>
-    <row r="53" spans="6:6" x14ac:dyDescent="0.3">
-      <c r="F53" s="43" t="s">
-        <v>65</v>
+    </row>
+    <row r="49" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F49" s="19"/>
+    </row>
+    <row r="52" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F52" s="24"/>
+    </row>
+    <row r="53" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F53" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="G21:J21"/>
     <mergeCell ref="F9:N9"/>
     <mergeCell ref="M11:N11"/>
     <mergeCell ref="Q11:R11"/>
     <mergeCell ref="P19:R19"/>
     <mergeCell ref="H20:K20"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="11" type="noConversion"/>
+  <pageMargins left="0" right="0" top="0.5" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="9" scale="73" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/QUOTATION TEMPLATE.xlsx
+++ b/templates/QUOTATION TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\Coding\Kintone\Projects\Clavano Excel Export v2.0\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FB296A-EC77-469D-8909-86E83E695AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BE451B1-A6E0-41C6-92BE-CF9AEF238699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C42AE516-AE06-4823-8788-BA3C80C7942B}"/>
   </bookViews>
@@ -470,6 +470,15 @@
     <xf numFmtId="43" fontId="14" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -492,15 +501,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -996,15 +996,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>207818</xdr:colOff>
+      <xdr:colOff>168404</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>103909</xdr:rowOff>
+      <xdr:rowOff>123616</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>10407</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>627890</xdr:colOff>
       <xdr:row>53</xdr:row>
-      <xdr:rowOff>51276</xdr:rowOff>
+      <xdr:rowOff>70983</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1033,8 +1033,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="314498" y="8417329"/>
-          <a:ext cx="1692349" cy="1410407"/>
+          <a:off x="273507" y="8807788"/>
+          <a:ext cx="1641900" cy="1471367"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1393,17 +1393,17 @@
   </cols>
   <sheetData>
     <row r="9" spans="6:19" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="32"/>
-      <c r="L9" s="32"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
@@ -1421,17 +1421,17 @@
       <c r="L11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M11" s="33" t="e">
+      <c r="M11" s="36" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="N11" s="33"/>
+      <c r="N11" s="36"/>
       <c r="O11" s="5"/>
       <c r="P11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
+      <c r="Q11" s="36"/>
+      <c r="R11" s="36"/>
       <c r="S11" s="5"/>
     </row>
     <row r="13" spans="6:19" x14ac:dyDescent="0.25">
@@ -1471,23 +1471,23 @@
       <c r="H18" s="25"/>
     </row>
     <row r="19" spans="6:19" x14ac:dyDescent="0.25">
-      <c r="P19" s="34" t="s">
+      <c r="P19" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="37"/>
     </row>
     <row r="20" spans="6:19" x14ac:dyDescent="0.25">
       <c r="F20" s="6" t="s">
         <v>7</v>
       </c>
       <c r="G20" s="7"/>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="36"/>
+      <c r="I20" s="38"/>
+      <c r="J20" s="38"/>
+      <c r="K20" s="39"/>
       <c r="L20" s="6" t="s">
         <v>9</v>
       </c>
@@ -1513,10 +1513,10 @@
       <c r="F21" s="9">
         <v>1</v>
       </c>
-      <c r="G21" s="29"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
-      <c r="J21" s="31"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="34"/>
       <c r="K21" s="11"/>
       <c r="L21" s="12" t="e">
         <f>#REF!</f>
@@ -1531,9 +1531,9 @@
         <v>#REF!</v>
       </c>
       <c r="O21" s="15"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="39"/>
+      <c r="P21" s="29"/>
+      <c r="Q21" s="30"/>
+      <c r="R21" s="31"/>
       <c r="S21" s="15"/>
     </row>
     <row r="22" spans="6:19" x14ac:dyDescent="0.25">
